--- a/PRTrack/PRTrack-sample-data.xlsx
+++ b/PRTrack/PRTrack-sample-data.xlsx
@@ -9,15 +9,17 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="READ ME" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRTrack - Permissions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRTrack - Requisitions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRTrack - LineItems" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRTrack - Attachments" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRTrack - ApproverRules" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRTrack - NWA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRTrack - Requisitions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRTrack - LineItems" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRTrack - Attachments" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PRTrack - Permissions'!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PRTrack - Requisitions'!$A$1:$R$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PRTrack - LineItems'!$A$1:$Z$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PRTrack - Attachments'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PRTrack - Requisitions'!$A$1:$R$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PRTrack - LineItems'!$A$1:$Z$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PRTrack - Attachments'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -507,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -638,6 +640,109 @@
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>PR-001 In procurement (pending approval), PR-002 In procurement (mixed lines), PR-003 On Hold, PR-004 Draft, PR-005 Rejected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>New lists (create in SharePoint before paste)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PRTrack - ApproverRules</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Columns: Title (text), Project (text), Category (text), RuleType (choice: Proceed, DOA), minamount (number), maxamount (number, optional), approvername (text), approveremail (text). Paste the ApproverRules sheet. Proceed is by category. DOA is by category plus dollar band. Replace sample bands with real IOC DOA if different.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PRTrack - NWA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Columns: Title (NWA number, text), Project (text), nwaname (text), cbsnumber (text), cbsname (text). Paste the NWA sheet. Replace sample names with real SAP labels when you have them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Permissions.Role</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Add choice value Project Controls. Keep Requester, Buyer, Approver, Viewer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LineItems new columns</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Add single line text: nwaname, cbsnumber, cbsname. Add stage choice: PO creation. Keep existing nwacode, origbudget, rembudget, quoted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Requisitions.prstatus</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Add choice value Pending PO. Keep Draft, Submitted, In procurement, Approved, Rejected, On Hold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Attachments list</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Already exists. App now reads it for chips. After paste, attach the real file on each SharePoint item if you want files, not just names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Paste order</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1) Permissions  2) ApproverRules  3) NWA  4) Requisitions  5) LineItems  6) Attachments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Studio data sources</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Add PRTrack - ApproverRules and PRTrack - NWA as SharePoint data sources, then re-export the seed .msapp so pack can see them.</t>
         </is>
       </c>
     </row>
@@ -655,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -962,6 +1067,33 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pc.controls@halrt.ca</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PC Controls</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Project Controls</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -970,6 +1102,579 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>RuleType</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>minamount</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>maxamount</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>approvername</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>approveremail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HaLRT-Proceed-Engineering</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Engineering/Subconsultant</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Proceed</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aaron Hoag</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>aaron.hoag@halrt.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HaLRT-Proceed-General</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>General Expenses</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Proceed</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>William Schreiber</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>william.schreiber@halrt.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HaLRT-Proceed-Construction</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Proceed</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Jeff Peroff</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>jeff.peroff@halrt.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HaLRT-DOA-Eng-0-50k</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Engineering/Subconsultant</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DOA</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Aaron Hoag</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>aaron.hoag@halrt.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HaLRT-DOA-Eng-50k</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Engineering/Subconsultant</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DOA</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tom Nierodzik</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>tom.nierodzik@halrt.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HaLRT-DOA-Gen-0-10k</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>General Expenses</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DOA</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>William Schreiber</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>william.schreiber@halrt.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HaLRT-DOA-Gen-10k</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>General Expenses</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DOA</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tom Nierodzik</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>tom.nierodzik@halrt.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HaLRT-DOA-Con-0-100k</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DOA</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Jeff Peroff</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>jeff.peroff@halrt.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HaLRT-DOA-Con-100k</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DOA</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tom Nierodzik</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>tom.nierodzik@halrt.ca</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>nwaname</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>cbsnumber</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cbsname</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2200-1140</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ADA Signage Design</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Design and Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1100-0500</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Site Overhead and General Expenses</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Indirect and G&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3300-2210</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Temporary Works - Shoring</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3300-1005</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Site Establishment - Fencing</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2200-0980</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HaLRT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Geotechnical Investigation</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Design and Engineering</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1536,13 +2241,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1654,17 +2359,17 @@
           <t>nwacode</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>origbudget</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rembudget</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>budgetstatus</t>
         </is>
@@ -1702,6 +2407,21 @@
       <c r="Z1" s="5" t="inlineStr">
         <is>
           <t>doacomment</t>
+        </is>
+      </c>
+      <c r="AA1" s="5" t="inlineStr">
+        <is>
+          <t>nwaname</t>
+        </is>
+      </c>
+      <c r="AB1" s="5" t="inlineStr">
+        <is>
+          <t>cbsnumber</t>
+        </is>
+      </c>
+      <c r="AC1" s="5" t="inlineStr">
+        <is>
+          <t>cbsname</t>
         </is>
       </c>
     </row>
@@ -1755,7 +2475,7 @@
       <c r="K2" s="9" t="n">
         <v>58900</v>
       </c>
-      <c r="L2" s="7" t="inlineStr"/>
+      <c r="L2" s="7" t="n"/>
       <c r="M2" s="7" t="inlineStr">
         <is>
           <t>Subconsultant</t>
@@ -1774,23 +2494,23 @@
           <t>2200-1140</t>
         </is>
       </c>
-      <c r="Q2" s="9" t="n">
+      <c r="Q2" t="n">
         <v>60000</v>
       </c>
-      <c r="R2" s="9" t="n">
+      <c r="R2" t="n">
         <v>41200</v>
       </c>
-      <c r="S2" s="7" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Within Approved Budget</t>
         </is>
       </c>
-      <c r="T2" s="7" t="inlineStr">
+      <c r="T2" s="9" t="inlineStr">
         <is>
           <t>Budget confirmed against ADA design estimate.</t>
         </is>
       </c>
-      <c r="U2" s="7" t="inlineStr">
+      <c r="U2" s="9" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -1800,7 +2520,7 @@
           <t>Tom Nierodzik</t>
         </is>
       </c>
-      <c r="W2" s="7" t="inlineStr"/>
+      <c r="W2" s="7" t="n"/>
       <c r="X2" s="7" t="inlineStr">
         <is>
           <t>Pending approval</t>
@@ -1811,7 +2531,22 @@
           <t>Tom Nierodzik</t>
         </is>
       </c>
-      <c r="Z2" s="7" t="inlineStr"/>
+      <c r="Z2" s="7" t="n"/>
+      <c r="AA2" s="7" t="inlineStr">
+        <is>
+          <t>ADA Signage Design</t>
+        </is>
+      </c>
+      <c r="AB2" s="7" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="AC2" s="7" t="inlineStr">
+        <is>
+          <t>Design and Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -1840,7 +2575,7 @@
       <c r="F3" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="n"/>
       <c r="H3" s="7" t="inlineStr">
         <is>
           <t>Amarachi</t>
@@ -1869,26 +2604,26 @@
           <t>PO within AD Phase estimate</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="7" t="n"/>
       <c r="O3" s="7" t="n"/>
       <c r="P3" s="7" t="inlineStr">
         <is>
           <t>1100-0500</t>
         </is>
       </c>
-      <c r="Q3" s="9" t="n">
+      <c r="Q3" t="n">
         <v>5000</v>
       </c>
-      <c r="R3" s="9" t="n">
+      <c r="R3" t="n">
         <v>2600</v>
       </c>
-      <c r="S3" s="7" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Within Approved Budget</t>
         </is>
       </c>
-      <c r="T3" s="7" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
+      <c r="T3" s="9" t="n"/>
+      <c r="U3" s="9" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -1898,7 +2633,7 @@
           <t>Tom Nierodzik</t>
         </is>
       </c>
-      <c r="W3" s="7" t="inlineStr"/>
+      <c r="W3" s="7" t="n"/>
       <c r="X3" s="7" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -1912,6 +2647,21 @@
       <c r="Z3" s="7" t="inlineStr">
         <is>
           <t>Approved.</t>
+        </is>
+      </c>
+      <c r="AA3" s="7" t="inlineStr">
+        <is>
+          <t>Site Overhead and General Expenses</t>
+        </is>
+      </c>
+      <c r="AB3" s="7" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="AC3" s="7" t="inlineStr">
+        <is>
+          <t>Indirect and G&amp;A</t>
         </is>
       </c>
     </row>
@@ -1942,7 +2692,7 @@
       <c r="F4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Amarachi</t>
@@ -1971,26 +2721,26 @@
           <t>PO within AD Phase estimate</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="7" t="n"/>
       <c r="O4" s="7" t="n"/>
       <c r="P4" s="7" t="inlineStr">
         <is>
           <t>1100-0500</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" t="n">
         <v>5000</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" t="n">
         <v>2600</v>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Within Approved Budget</t>
         </is>
       </c>
-      <c r="T4" s="7" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
+      <c r="T4" s="9" t="n"/>
+      <c r="U4" s="9" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -2000,7 +2750,7 @@
           <t>Tom Nierodzik</t>
         </is>
       </c>
-      <c r="W4" s="7" t="inlineStr"/>
+      <c r="W4" s="7" t="n"/>
       <c r="X4" s="7" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -2014,6 +2764,21 @@
       <c r="Z4" s="7" t="inlineStr">
         <is>
           <t>Approved.</t>
+        </is>
+      </c>
+      <c r="AA4" s="7" t="inlineStr">
+        <is>
+          <t>Site Overhead and General Expenses</t>
+        </is>
+      </c>
+      <c r="AB4" s="7" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="AC4" s="7" t="inlineStr">
+        <is>
+          <t>Indirect and G&amp;A</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2832,7 @@
       <c r="K5" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="L5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="n"/>
       <c r="M5" s="7" t="inlineStr">
         <is>
           <t>PO within AD Phase estimate</t>
@@ -2086,19 +2851,19 @@
           <t>1100-0500</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" t="n">
         <v>5000</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" t="n">
         <v>2600</v>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Within Approved Budget</t>
         </is>
       </c>
-      <c r="T5" s="7" t="inlineStr"/>
-      <c r="U5" s="7" t="inlineStr">
+      <c r="T5" s="9" t="n"/>
+      <c r="U5" s="9" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -2108,7 +2873,7 @@
           <t>Tom Nierodzik</t>
         </is>
       </c>
-      <c r="W5" s="7" t="inlineStr"/>
+      <c r="W5" s="7" t="n"/>
       <c r="X5" s="7" t="inlineStr">
         <is>
           <t>Pending approval</t>
@@ -2119,7 +2884,22 @@
           <t>Tom Nierodzik</t>
         </is>
       </c>
-      <c r="Z5" s="7" t="inlineStr"/>
+      <c r="Z5" s="7" t="n"/>
+      <c r="AA5" s="7" t="inlineStr">
+        <is>
+          <t>Site Overhead and General Expenses</t>
+        </is>
+      </c>
+      <c r="AB5" s="7" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="AC5" s="7" t="inlineStr">
+        <is>
+          <t>Indirect and G&amp;A</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2148,7 +2928,7 @@
       <c r="F6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Ali</t>
@@ -2167,32 +2947,32 @@
       <c r="K6" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="L6" s="7" t="inlineStr"/>
+      <c r="L6" s="7" t="n"/>
       <c r="M6" s="7" t="inlineStr">
         <is>
           <t>PO within AD Phase estimate</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="7" t="n"/>
       <c r="O6" s="7" t="n"/>
       <c r="P6" s="7" t="inlineStr">
         <is>
           <t>1100-0500</t>
         </is>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" t="n">
         <v>5000</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" t="n">
         <v>2600</v>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Within Approved Budget</t>
         </is>
       </c>
-      <c r="T6" s="7" t="inlineStr"/>
-      <c r="U6" s="7" t="inlineStr">
+      <c r="T6" s="9" t="n"/>
+      <c r="U6" s="9" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -2202,7 +2982,7 @@
           <t>Tom Nierodzik</t>
         </is>
       </c>
-      <c r="W6" s="7" t="inlineStr"/>
+      <c r="W6" s="7" t="n"/>
       <c r="X6" s="7" t="inlineStr">
         <is>
           <t>Sourcing</t>
@@ -2213,7 +2993,22 @@
           <t>Tom Nierodzik</t>
         </is>
       </c>
-      <c r="Z6" s="7" t="inlineStr"/>
+      <c r="Z6" s="7" t="n"/>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>Site Overhead and General Expenses</t>
+        </is>
+      </c>
+      <c r="AB6" s="7" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="AC6" s="7" t="inlineStr">
+        <is>
+          <t>Indirect and G&amp;A</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2242,7 +3037,7 @@
       <c r="F7" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Ali</t>
@@ -2261,7 +3056,7 @@
       <c r="K7" s="9" t="n">
         <v>420000</v>
       </c>
-      <c r="L7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="n"/>
       <c r="M7" s="7" t="inlineStr">
         <is>
           <t>Alternative Procurement</t>
@@ -2280,23 +3075,23 @@
           <t>3300-2210</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" t="n">
         <v>620000</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Requires Budget Adjustment</t>
         </is>
       </c>
-      <c r="T7" s="7" t="inlineStr">
+      <c r="T7" s="9" t="inlineStr">
         <is>
           <t>Over estimate — escalated to Design &amp; Construction Segment Integration Director.</t>
         </is>
       </c>
-      <c r="U7" s="7" t="inlineStr">
+      <c r="U7" s="9" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -2306,7 +3101,7 @@
           <t>Tom Nierodzik</t>
         </is>
       </c>
-      <c r="W7" s="7" t="inlineStr"/>
+      <c r="W7" s="7" t="n"/>
       <c r="X7" s="7" t="inlineStr">
         <is>
           <t>On hold</t>
@@ -2320,6 +3115,21 @@
       <c r="Z7" s="7" t="inlineStr">
         <is>
           <t>On hold pending budget adjustment.</t>
+        </is>
+      </c>
+      <c r="AA7" s="7" t="inlineStr">
+        <is>
+          <t>Temporary Works - Shoring</t>
+        </is>
+      </c>
+      <c r="AB7" s="7" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="AC7" s="7" t="inlineStr">
+        <is>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -2373,7 +3183,7 @@
       <c r="K8" s="9" t="n">
         <v>221500</v>
       </c>
-      <c r="L8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="n"/>
       <c r="M8" s="7" t="inlineStr">
         <is>
           <t>Alternative Procurement</t>
@@ -2390,23 +3200,23 @@
           <t>3300-2210</t>
         </is>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" t="n">
         <v>620000</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Requires Budget Adjustment</t>
         </is>
       </c>
-      <c r="T8" s="7" t="inlineStr">
+      <c r="T8" s="9" t="inlineStr">
         <is>
           <t>Over estimate — escalated to Design &amp; Construction Segment Integration Director.</t>
         </is>
       </c>
-      <c r="U8" s="7" t="inlineStr">
+      <c r="U8" s="9" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -2416,7 +3226,7 @@
           <t>Tom Nierodzik</t>
         </is>
       </c>
-      <c r="W8" s="7" t="inlineStr"/>
+      <c r="W8" s="7" t="n"/>
       <c r="X8" s="7" t="inlineStr">
         <is>
           <t>On hold</t>
@@ -2430,6 +3240,21 @@
       <c r="Z8" s="7" t="inlineStr">
         <is>
           <t>On hold pending budget adjustment.</t>
+        </is>
+      </c>
+      <c r="AA8" s="7" t="inlineStr">
+        <is>
+          <t>Temporary Works - Shoring</t>
+        </is>
+      </c>
+      <c r="AB8" s="7" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="AC8" s="7" t="inlineStr">
+        <is>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -2460,43 +3285,43 @@
       <c r="F9" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="G9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="n"/>
       <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
       <c r="K9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="n"/>
       <c r="M9" s="7" t="inlineStr">
         <is>
           <t>PO within AD Phase estimate</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="n"/>
       <c r="O9" s="7" t="n"/>
       <c r="P9" s="7" t="inlineStr">
         <is>
           <t>3300-1005</t>
         </is>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" t="n">
         <v>22000</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" t="n">
         <v>22000</v>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Within Approved Budget</t>
         </is>
       </c>
-      <c r="T9" s="7" t="inlineStr"/>
-      <c r="U9" s="7" t="inlineStr">
+      <c r="T9" s="9" t="n"/>
+      <c r="U9" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2506,7 +3331,7 @@
           <t>Tom Nierodzik</t>
         </is>
       </c>
-      <c r="W9" s="7" t="inlineStr"/>
+      <c r="W9" s="7" t="n"/>
       <c r="X9" s="7" t="inlineStr">
         <is>
           <t>Pending proceed</t>
@@ -2517,7 +3342,22 @@
           <t>Tom Nierodzik</t>
         </is>
       </c>
-      <c r="Z9" s="7" t="inlineStr"/>
+      <c r="Z9" s="7" t="n"/>
+      <c r="AA9" s="7" t="inlineStr">
+        <is>
+          <t>Site Establishment - Fencing</t>
+        </is>
+      </c>
+      <c r="AB9" s="7" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="AC9" s="7" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -2569,32 +3409,32 @@
       <c r="K10" s="9" t="n">
         <v>11800</v>
       </c>
-      <c r="L10" s="7" t="inlineStr"/>
+      <c r="L10" s="7" t="n"/>
       <c r="M10" s="7" t="inlineStr">
         <is>
           <t>Subconsultant</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="7" t="n"/>
       <c r="O10" s="7" t="n"/>
       <c r="P10" s="7" t="inlineStr">
         <is>
           <t>2200-0980</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" t="n">
         <v>15000</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" t="n">
         <v>3200</v>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>Within Approved Budget</t>
         </is>
       </c>
-      <c r="T10" s="7" t="inlineStr"/>
-      <c r="U10" s="7" t="inlineStr">
+      <c r="T10" s="9" t="n"/>
+      <c r="U10" s="9" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -2604,7 +3444,7 @@
           <t>Tom Nierodzik</t>
         </is>
       </c>
-      <c r="W10" s="7" t="inlineStr"/>
+      <c r="W10" s="7" t="n"/>
       <c r="X10" s="7" t="inlineStr">
         <is>
           <t>Rejected</t>
@@ -2618,6 +3458,21 @@
       <c r="Z10" s="7" t="inlineStr">
         <is>
           <t>Duplicate of PR-003 scope.</t>
+        </is>
+      </c>
+      <c r="AA10" s="7" t="inlineStr">
+        <is>
+          <t>Geotechnical Investigation</t>
+        </is>
+      </c>
+      <c r="AB10" s="7" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="AC10" s="7" t="inlineStr">
+        <is>
+          <t>Design and Engineering</t>
         </is>
       </c>
     </row>
@@ -2627,7 +3482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
